--- a/astro-site/public/dl/coffee-shop-checklist-templates/02-cafe-kitchen-pastry-case-checklists.xlsx
+++ b/astro-site/public/dl/coffee-shop-checklist-templates/02-cafe-kitchen-pastry-case-checklists.xlsx
@@ -170,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -258,6 +258,10 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1153,7 +1157,7 @@
       </c>
       <c r="B16" s="32" t="inlineStr">
         <is>
-          <t>Check egg doneness: poached, scrambled, fried</t>
+          <t>Check egg doneness: poached, scrambled, fried (runny yolks need the consumer advisory on the menu unless the eggs are pasteurized, FDA 3-603.11)</t>
         </is>
       </c>
       <c r="C16" s="29" t="inlineStr">
@@ -2676,9 +2680,9 @@
       <c r="A23" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="32" t="inlineStr">
-        <is>
-          <t>Clear the case; store everything in the walk-in</t>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>Clear the case: TCS items (custards, cheesecake, dairy fillings) to the cooler at 41 °F or below; dry baked goods covered and dated</t>
         </is>
       </c>
       <c r="C23" s="29" t="inlineStr">

--- a/astro-site/public/dl/coffee-shop-checklist-templates/02-cafe-kitchen-pastry-case-checklists.xlsx
+++ b/astro-site/public/dl/coffee-shop-checklist-templates/02-cafe-kitchen-pastry-case-checklists.xlsx
@@ -980,9 +980,9 @@
       <c r="A9" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>Smoked salmon and fish served raw — parasite destruction: get the supplier's freezing record (frozen at −4 °F or below for 7 days, or −31 °F or below until solid + 15 h) or freeze it yourself; log the lot and keep the record 90 days (FDA Food Code 3-402.11)</t>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Smoked salmon and fish served raw — parasite destruction (FDA Food Code 3-402.11): get the supplier's freezing record (frozen at −4 °F or below for 7 days; or at −31 °F or below until solid, then 15 h at −31 °F or below or 24 h at −4 °F or below) or freeze it yourself; log the lot and keep the record 90 days (FDA Food Code 3-402.12)</t>
         </is>
       </c>
       <c r="C9" s="29" t="inlineStr">
